--- a/ProjectManager/Models/DatabaseStructure.xlsx
+++ b/ProjectManager/Models/DatabaseStructure.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johns\source\repos\iamJohnnySam\nexus\ProjectManager\Models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MT-0051\source\repos\iamJohnnySam\nexus\ProjectManager\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D5DFF4-BD88-4294-A6C8-EAF373C5D8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E485174-4253-42B4-8707-6EBC900E74F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DFBCF54E-DA7A-452C-A795-39752D2D19EC}"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" xr2:uid="{DFBCF54E-DA7A-452C-A795-39752D2D19EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
   <si>
     <t>Project</t>
   </si>
   <si>
-    <t>ProjectID</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -51,24 +48,12 @@
     <t>Customer</t>
   </si>
   <si>
-    <t>CustomerID</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
     <t>DesignCode</t>
   </si>
   <si>
-    <t>string []</t>
-  </si>
-  <si>
-    <t>PreviousCodes</t>
-  </si>
-  <si>
-    <t>POCodes</t>
-  </si>
-  <si>
     <t>ProjectPriority</t>
   </si>
   <si>
@@ -84,33 +69,21 @@
     <t>Product</t>
   </si>
   <si>
-    <t>ProductID</t>
-  </si>
-  <si>
     <t>ProductName</t>
   </si>
   <si>
     <t>Module</t>
   </si>
   <si>
-    <t>ModuleID</t>
-  </si>
-  <si>
     <t>ModuleName</t>
   </si>
   <si>
     <t>int []</t>
   </si>
   <si>
-    <t>ModuleIDs</t>
-  </si>
-  <si>
     <t>Designation</t>
   </si>
   <si>
-    <t>DesignationID</t>
-  </si>
-  <si>
     <t>DesignationName</t>
   </si>
   <si>
@@ -120,18 +93,12 @@
     <t>Employee</t>
   </si>
   <si>
-    <t>EmployeeID</t>
-  </si>
-  <si>
     <t>EmployeeName</t>
   </si>
   <si>
     <t>Grade</t>
   </si>
   <si>
-    <t>GradeID</t>
-  </si>
-  <si>
     <t>GradeName</t>
   </si>
   <si>
@@ -153,24 +120,12 @@
     <t>LeaveDate</t>
   </si>
   <si>
-    <t>ReplacedEmployeeID</t>
-  </si>
-  <si>
     <t>TaskItem</t>
   </si>
   <si>
-    <t>TaskID</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
-    <t>int [string]</t>
-  </si>
-  <si>
-    <t>Responsible</t>
-  </si>
-  <si>
     <t>CreatedOn</t>
   </si>
   <si>
@@ -183,18 +138,12 @@
     <t>int?</t>
   </si>
   <si>
-    <t>ParentTaskID</t>
-  </si>
-  <si>
     <t>ReviewItem</t>
   </si>
   <si>
     <t>ReviewPoint</t>
   </si>
   <si>
-    <t>ReviewItemID</t>
-  </si>
-  <si>
     <t>Approved</t>
   </si>
   <si>
@@ -204,13 +153,64 @@
     <t>ReviewComments</t>
   </si>
   <si>
-    <t>ReviewResponsibleID</t>
-  </si>
-  <si>
-    <t>ReviewPointID</t>
-  </si>
-  <si>
     <t>ReviewDescription</t>
+  </si>
+  <si>
+    <t>TaskItemResponsibility</t>
+  </si>
+  <si>
+    <t>EmployeeId</t>
+  </si>
+  <si>
+    <t>PreviousProjectCodes</t>
+  </si>
+  <si>
+    <t>ProjectCode</t>
+  </si>
+  <si>
+    <t>ProjectPCodes</t>
+  </si>
+  <si>
+    <t>POCode</t>
+  </si>
+  <si>
+    <t>ProjectId</t>
+  </si>
+  <si>
+    <t>CustomerId</t>
+  </si>
+  <si>
+    <t>ProductId</t>
+  </si>
+  <si>
+    <t>ModuleId</t>
+  </si>
+  <si>
+    <t>DesignationId</t>
+  </si>
+  <si>
+    <t>GradeId</t>
+  </si>
+  <si>
+    <t>ModuleIds</t>
+  </si>
+  <si>
+    <t>ReplacedEmployeeId</t>
+  </si>
+  <si>
+    <t>TaskId</t>
+  </si>
+  <si>
+    <t>ReviewItemId</t>
+  </si>
+  <si>
+    <t>ReviewPointId</t>
+  </si>
+  <si>
+    <t>ParentTaskId</t>
+  </si>
+  <si>
+    <t>ReviewResponsibleId</t>
   </si>
 </sst>
 </file>
@@ -268,10 +268,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -644,7 +643,7 @@
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>857250</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -693,16 +692,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>904875</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>790575</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -717,8 +716,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="2447925" y="485775"/>
-          <a:ext cx="5657850" cy="3800475"/>
+          <a:off x="8296275" y="485775"/>
+          <a:ext cx="733425" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -757,8 +756,8 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -775,7 +774,7 @@
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
           <a:off x="1219200" y="447675"/>
-          <a:ext cx="2886075" cy="3448050"/>
+          <a:ext cx="2943225" cy="3067050"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -815,7 +814,7 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -866,13 +865,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -929,7 +928,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -976,13 +975,184 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>771525</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{270DD994-E186-4292-A486-000DA5A3B309}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1381125" y="3314700"/>
+          <a:ext cx="6696075" cy="38100"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+          <a:headEnd type="oval" w="med" len="med"/>
+          <a:tailEnd type="oval" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9512FF2-EE4A-41FB-BEEB-8AA24C0C2252}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1333500" y="466725"/>
+          <a:ext cx="8572500" cy="2828925"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+          <a:headEnd type="oval" w="med" len="med"/>
+          <a:tailEnd type="oval" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>781050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EF51FC2-27D1-8676-B19F-2E4863D5E0FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1390650" y="447675"/>
+          <a:ext cx="10582275" cy="2886075"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+          <a:headEnd type="oval" w="med" len="med"/>
+          <a:tailEnd type="oval" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1020,7 +1190,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1126,7 +1296,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1268,7 +1438,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1276,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{369982B9-39A9-4305-92B7-8D6E13ECF4BC}">
-  <dimension ref="A2:W27"/>
+  <dimension ref="B2:U24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
@@ -1297,718 +1467,387 @@
     <col min="22" max="22" width="1.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="T2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="3"/>
-      <c r="N2" s="3" t="s">
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>4</v>
+      </c>
+      <c r="R4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" t="s">
+        <v>4</v>
+      </c>
+      <c r="U4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>4</v>
+      </c>
+      <c r="R5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="Q2" s="3" t="s">
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="N17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="Q17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>4</v>
+      </c>
+      <c r="R19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="3"/>
-      <c r="T2" s="3" t="s">
+      <c r="C21" t="s">
         <v>30</v>
       </c>
-      <c r="U2" s="3"/>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" s="2" t="s">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
         <v>31</v>
       </c>
-      <c r="V3" s="2"/>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R4" s="2" t="s">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="U4" s="2" t="s">
+      <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="V4" s="2"/>
+      <c r="E23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="U5" s="2" t="s">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>33</v>
       </c>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="C24" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="E24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
